--- a/data/energy_calcs_test.xlsx
+++ b/data/energy_calcs_test.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tacaro/Documents/GitHub/Oman-2023/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B9C05FE-4295-074A-BA3C-AA05F0AAD421}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6367DE31-612B-4143-83C3-A347438D6EF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30240" yWindow="500" windowWidth="38400" windowHeight="21100" xr2:uid="{8F696B31-6E43-4943-9230-EFFA872EF783}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" xr2:uid="{8F696B31-6E43-4943-9230-EFFA872EF783}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="18">
   <si>
     <t>J per tonne H2</t>
   </si>
@@ -78,14 +78,27 @@
   </si>
   <si>
     <t>J/tonne H2</t>
+  </si>
+  <si>
+    <t>Converting canovas to J/tonne H2</t>
+  </si>
+  <si>
+    <t>kcal/mol e-</t>
+  </si>
+  <si>
+    <t>kJ/mol e-</t>
+  </si>
+  <si>
+    <t>e- per H2</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="166" formatCode="0.0000E+00"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.0000E+00"/>
+    <numFmt numFmtId="166" formatCode="0.000E+00"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -123,7 +136,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -140,6 +153,7 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -475,11 +489,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8F358F1-0A3B-0947-AA42-B0E27BF6B20A}">
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="21.5" customWidth="1"/>
     <col min="2" max="2" width="17.83203125" customWidth="1"/>
+    <col min="8" max="8" width="12.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
@@ -496,7 +511,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
@@ -590,6 +605,68 @@
       <c r="B11" s="8">
         <f>A11*1000000</f>
         <v>23920000000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A15" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16" t="s">
+        <v>17</v>
+      </c>
+      <c r="D16" t="s">
+        <v>4</v>
+      </c>
+      <c r="E16" t="s">
+        <v>3</v>
+      </c>
+      <c r="F16" t="s">
+        <v>2</v>
+      </c>
+      <c r="G16" t="s">
+        <v>12</v>
+      </c>
+      <c r="H16" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <v>3</v>
+      </c>
+      <c r="B17">
+        <f>A17*4.184</f>
+        <v>12.552</v>
+      </c>
+      <c r="C17">
+        <v>2</v>
+      </c>
+      <c r="D17">
+        <f>B17*C17</f>
+        <v>25.103999999999999</v>
+      </c>
+      <c r="E17">
+        <f>D17*1000</f>
+        <v>25104</v>
+      </c>
+      <c r="F17">
+        <v>2</v>
+      </c>
+      <c r="G17">
+        <f>E17/F17</f>
+        <v>12552</v>
+      </c>
+      <c r="H17" s="9">
+        <f>G17*1000000</f>
+        <v>12552000000</v>
       </c>
     </row>
   </sheetData>
